--- a/School_docs/Premchand Mahto Inter College/Arts/session 2026-28 Arts.xlsx
+++ b/School_docs/Premchand Mahto Inter College/Arts/session 2026-28 Arts.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="317">
   <si>
     <t>DATE OF BIRTH</t>
   </si>
@@ -832,6 +832,141 @@
   </si>
   <si>
     <t>OBC</t>
+  </si>
+  <si>
+    <t>NITESH MAHTO</t>
+  </si>
+  <si>
+    <t>NAGESHWAR MAHTO</t>
+  </si>
+  <si>
+    <t>SHIVAN DEVI</t>
+  </si>
+  <si>
+    <t>ABUJAR ANSARI</t>
+  </si>
+  <si>
+    <t>TAJUDDIN ANSARI</t>
+  </si>
+  <si>
+    <t>MUSTARI KHATOON</t>
+  </si>
+  <si>
+    <t>PRADEEP BADING</t>
+  </si>
+  <si>
+    <t>MANUAL BADING</t>
+  </si>
+  <si>
+    <t>BISWASI BADING</t>
+  </si>
+  <si>
+    <t>LALDEV MUNDA</t>
+  </si>
+  <si>
+    <t>SABITA DEVI</t>
+  </si>
+  <si>
+    <t>RAHUL ORAON</t>
+  </si>
+  <si>
+    <t>RAJBALAM ORAON</t>
+  </si>
+  <si>
+    <t>HARSHIT KUMAR</t>
+  </si>
+  <si>
+    <t>RAJESH RAM</t>
+  </si>
+  <si>
+    <t>HARMAN ORAON</t>
+  </si>
+  <si>
+    <t>BANDHU ORAON</t>
+  </si>
+  <si>
+    <t>MOHIT ORAON</t>
+  </si>
+  <si>
+    <t>BUDHWA ORAON</t>
+  </si>
+  <si>
+    <t>RUBIYA DEVI</t>
+  </si>
+  <si>
+    <t>SUSHMITA KUMARI</t>
+  </si>
+  <si>
+    <t>GANESH MAHLI</t>
+  </si>
+  <si>
+    <t>SONAMANI DEVI</t>
+  </si>
+  <si>
+    <t>NIOS</t>
+  </si>
+  <si>
+    <t>FAIZAN KHAN</t>
+  </si>
+  <si>
+    <t>IRFAN KHAN</t>
+  </si>
+  <si>
+    <t>NASINA KHATUN</t>
+  </si>
+  <si>
+    <t>NAMISH ORAON</t>
+  </si>
+  <si>
+    <t>MANTU ORAON</t>
+  </si>
+  <si>
+    <t>CHIRAG KUMAR SAHU</t>
+  </si>
+  <si>
+    <t>SURINDER SAHU</t>
+  </si>
+  <si>
+    <t>MUSKAN KUMARI</t>
+  </si>
+  <si>
+    <t>RAJU ORAON</t>
+  </si>
+  <si>
+    <t>SAHZADI PARWEEN</t>
+  </si>
+  <si>
+    <t>SAMIM ANSARI</t>
+  </si>
+  <si>
+    <t>SAMIMA KHATOON</t>
+  </si>
+  <si>
+    <t>ARMAN ANSARI</t>
+  </si>
+  <si>
+    <t>GULAM NABI</t>
+  </si>
+  <si>
+    <t>RASHIDA KHATOON</t>
+  </si>
+  <si>
+    <t>SAHBAJ ANSARI</t>
+  </si>
+  <si>
+    <t>JARINA KHATOON</t>
+  </si>
+  <si>
+    <t>HASIM ANSARI</t>
+  </si>
+  <si>
+    <t>ANISH ORAON</t>
+  </si>
+  <si>
+    <t>GUMAN ORAON</t>
+  </si>
+  <si>
+    <t>SUMAN ORAON</t>
   </si>
 </sst>
 </file>
@@ -1199,12 +1334,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="7.5703125" customWidth="1"/>
     <col min="6" max="6" width="14" style="2" customWidth="1"/>
@@ -1219,7 +1354,7 @@
       <c r="A1" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>265</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -1254,7 +1389,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1271,6 +1406,9 @@
       </c>
       <c r="G2" s="2">
         <v>9798861420</v>
+      </c>
+      <c r="H2" s="1">
+        <v>470713022497</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>6</v>
@@ -1283,7 +1421,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1315,7 +1453,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1347,7 +1485,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1379,7 +1517,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1411,7 +1549,7 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1440,7 +1578,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1472,7 +1610,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1504,7 +1642,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1533,7 +1671,7 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1562,7 +1700,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1594,7 +1732,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1626,7 +1764,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1658,7 +1796,7 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1690,7 +1828,7 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1722,7 +1860,7 @@
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1754,7 +1892,7 @@
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1786,7 +1924,7 @@
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1812,7 +1950,7 @@
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1841,7 +1979,7 @@
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1873,7 +2011,7 @@
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1905,7 +2043,7 @@
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1937,7 +2075,7 @@
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1969,7 +2107,7 @@
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -1998,7 +2136,7 @@
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2030,7 +2168,7 @@
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2059,7 +2197,7 @@
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2091,7 +2229,7 @@
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2123,7 +2261,7 @@
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2155,7 +2293,7 @@
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2187,7 +2325,7 @@
       <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2219,7 +2357,7 @@
       <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2251,7 +2389,7 @@
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2280,7 +2418,7 @@
       <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -2312,7 +2450,7 @@
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2341,7 +2479,7 @@
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -2373,7 +2511,7 @@
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2402,7 +2540,7 @@
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2431,7 +2569,7 @@
       <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -2460,7 +2598,7 @@
       <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -2486,7 +2624,7 @@
       <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -2518,7 +2656,7 @@
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -2550,7 +2688,7 @@
       <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -2582,7 +2720,7 @@
       <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -2614,7 +2752,7 @@
       <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -2646,7 +2784,7 @@
       <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -2678,7 +2816,7 @@
       <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -2707,7 +2845,7 @@
       <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -2739,7 +2877,7 @@
       <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -2768,7 +2906,7 @@
       <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -2797,7 +2935,7 @@
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -2823,7 +2961,7 @@
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -2855,7 +2993,7 @@
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2884,7 +3022,7 @@
       <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2916,7 +3054,7 @@
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -2945,7 +3083,7 @@
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -2977,7 +3115,7 @@
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -3006,7 +3144,7 @@
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -3032,7 +3170,7 @@
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -3052,13 +3190,16 @@
       </c>
       <c r="I60" s="1">
         <v>732584179814</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C61" s="2" t="s">
@@ -3090,7 +3231,7 @@
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -3116,7 +3257,7 @@
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -3139,7 +3280,7 @@
       <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -3171,7 +3312,7 @@
       <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -3203,7 +3344,7 @@
       <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -3235,7 +3376,7 @@
       <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -3267,7 +3408,7 @@
       <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -3296,7 +3437,7 @@
       <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -3328,7 +3469,7 @@
       <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -3360,7 +3501,7 @@
       <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -3392,7 +3533,7 @@
       <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
         <v>208</v>
       </c>
       <c r="C72" s="2" t="s">
@@ -3424,7 +3565,7 @@
       <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
         <v>210</v>
       </c>
       <c r="C73" s="2" t="s">
@@ -3456,7 +3597,7 @@
       <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -3488,7 +3629,7 @@
       <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
         <v>215</v>
       </c>
       <c r="C75" s="2" t="s">
@@ -3520,7 +3661,7 @@
       <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -3537,6 +3678,9 @@
       </c>
       <c r="H76" s="1">
         <v>266766285310</v>
+      </c>
+      <c r="I76" s="1">
+        <v>674161110068</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>6</v>
@@ -3549,7 +3693,7 @@
       <c r="A77" s="2">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>220</v>
       </c>
       <c r="C77" s="2" t="s">
@@ -3581,7 +3725,7 @@
       <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C78" s="2" t="s">
@@ -3610,7 +3754,7 @@
       <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="2" t="s">
         <v>226</v>
       </c>
       <c r="C79" s="2" t="s">
@@ -3642,7 +3786,7 @@
       <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -3674,7 +3818,7 @@
       <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>231</v>
       </c>
       <c r="C81" s="2" t="s">
@@ -3691,13 +3835,16 @@
       </c>
       <c r="H81" s="1">
         <v>523615512798</v>
+      </c>
+      <c r="I81" s="1">
+        <v>436408354496</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="2" t="s">
         <v>234</v>
       </c>
       <c r="C82" s="2" t="s">
@@ -3729,7 +3876,7 @@
       <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>237</v>
       </c>
       <c r="C83" s="2" t="s">
@@ -3758,7 +3905,7 @@
       <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>240</v>
       </c>
       <c r="C84" s="2" t="s">
@@ -3787,7 +3934,7 @@
       <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2" t="s">
         <v>243</v>
       </c>
       <c r="C85" s="2" t="s">
@@ -3804,6 +3951,9 @@
       </c>
       <c r="H85" s="1">
         <v>415701592196</v>
+      </c>
+      <c r="I85" s="1">
+        <v>802104482076</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>6</v>
@@ -3816,7 +3966,7 @@
       <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>246</v>
       </c>
       <c r="C86" s="2" t="s">
@@ -3833,6 +3983,9 @@
       </c>
       <c r="H86" s="1">
         <v>553252519538</v>
+      </c>
+      <c r="I86" s="1">
+        <v>754983570249</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>6</v>
@@ -3845,7 +3998,7 @@
       <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
         <v>249</v>
       </c>
       <c r="C87" s="2" t="s">
@@ -3868,7 +4021,7 @@
       <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2" t="s">
         <v>252</v>
       </c>
       <c r="C88" s="2" t="s">
@@ -3900,7 +4053,7 @@
       <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>255</v>
       </c>
       <c r="C89" s="2" t="s">
@@ -3932,7 +4085,7 @@
       <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>258</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -3958,7 +4111,7 @@
       <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2" t="s">
         <v>261</v>
       </c>
       <c r="C91" s="2" t="s">
@@ -3984,6 +4137,530 @@
       </c>
       <c r="K91" s="3">
         <v>49.6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F92" s="8">
+        <v>40248</v>
+      </c>
+      <c r="G92" s="2">
+        <v>6203475783</v>
+      </c>
+      <c r="H92" s="1">
+        <v>409001189367</v>
+      </c>
+      <c r="I92" s="1">
+        <v>707722966626</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F93" s="8">
+        <v>40273</v>
+      </c>
+      <c r="G93" s="2">
+        <v>9798006384</v>
+      </c>
+      <c r="H93" s="1">
+        <v>725876136633</v>
+      </c>
+      <c r="I93" s="1">
+        <v>907590196390</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K93" s="3">
+        <v>64.400000000000006</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F94" s="8">
+        <v>39814</v>
+      </c>
+      <c r="G94" s="2">
+        <v>7292989668</v>
+      </c>
+      <c r="H94" s="1">
+        <v>510200990563</v>
+      </c>
+      <c r="I94" s="1">
+        <v>422447062754</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F95" s="8">
+        <v>40062</v>
+      </c>
+      <c r="G95" s="2">
+        <v>8271683033</v>
+      </c>
+      <c r="H95" s="1">
+        <v>360728712576</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K95" s="3">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="8">
+        <v>39887</v>
+      </c>
+      <c r="G96" s="2">
+        <v>8271712072</v>
+      </c>
+      <c r="H96" s="1">
+        <v>472193978690</v>
+      </c>
+      <c r="I96" s="1">
+        <v>670683902685</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K96" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F97" s="8">
+        <v>39249</v>
+      </c>
+      <c r="G97" s="2">
+        <v>8210637889</v>
+      </c>
+      <c r="H97" s="1">
+        <v>997067569701</v>
+      </c>
+      <c r="I97" s="1">
+        <v>357251899079</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K97" s="3">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F98" s="8">
+        <v>40022</v>
+      </c>
+      <c r="G98" s="2">
+        <v>8969678040</v>
+      </c>
+      <c r="H98" s="1">
+        <v>292418508746</v>
+      </c>
+      <c r="I98" s="1">
+        <v>830378174464</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K98" s="3">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F99" s="8">
+        <v>39505</v>
+      </c>
+      <c r="G99" s="2">
+        <v>8789859807</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K99" s="3">
+        <v>70.599999999999994</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F100" s="8">
+        <v>39972</v>
+      </c>
+      <c r="G100" s="2">
+        <v>9241908609</v>
+      </c>
+      <c r="H100" s="1">
+        <v>413774638788</v>
+      </c>
+      <c r="I100" s="1">
+        <v>865493657565</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K100" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" s="8">
+        <v>39161</v>
+      </c>
+      <c r="G101" s="2">
+        <v>8797789161</v>
+      </c>
+      <c r="H101" s="1">
+        <v>428348433647</v>
+      </c>
+      <c r="I101" s="1">
+        <v>830419537571</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K101" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="8">
+        <v>40734</v>
+      </c>
+      <c r="G102" s="2">
+        <v>9199562751</v>
+      </c>
+      <c r="H102" s="1">
+        <v>676441225859</v>
+      </c>
+      <c r="I102" s="1">
+        <v>540917400528</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K102" s="3">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="2">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F103" s="8">
+        <v>40524</v>
+      </c>
+      <c r="G103" s="2">
+        <v>9973489208</v>
+      </c>
+      <c r="H103" s="1">
+        <v>997527919503</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K103" s="3">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F104" s="8">
+        <v>40250</v>
+      </c>
+      <c r="G104" s="2">
+        <v>8434465361</v>
+      </c>
+      <c r="H104" s="1">
+        <v>407940268072</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K104" s="3">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="2">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F105" s="8">
+        <v>38579</v>
+      </c>
+      <c r="G105" s="2">
+        <v>6202889087</v>
+      </c>
+      <c r="H105" s="1">
+        <v>607589919185</v>
+      </c>
+      <c r="I105" s="1">
+        <v>428539798538</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K105" s="3">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F106" s="8">
+        <v>40091</v>
+      </c>
+      <c r="G106" s="2">
+        <v>9608621587</v>
+      </c>
+      <c r="H106" s="1">
+        <v>451726266646</v>
+      </c>
+      <c r="I106" s="1">
+        <v>396736021053</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K106" s="3">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="2">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F107" s="8">
+        <v>39940</v>
+      </c>
+      <c r="G107" s="2">
+        <v>7979748281</v>
+      </c>
+      <c r="H107" s="1">
+        <v>705082362168</v>
+      </c>
+      <c r="I107" s="1">
+        <v>542080012399</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K107" s="3">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F108" s="8">
+        <v>39814</v>
+      </c>
+      <c r="G108" s="2">
+        <v>9798392346</v>
+      </c>
+      <c r="H108" s="1">
+        <v>621009678169</v>
+      </c>
+      <c r="I108" s="1">
+        <v>485261631977</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K108" s="3">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
